--- a/DateBase/orders/Nha Thu_2026-5-22.xlsx
+++ b/DateBase/orders/Nha Thu_2026-5-22.xlsx
@@ -1203,6 +1203,9 @@
       <c r="G2" t="str">
         <v>0101015202015555555552020205310351015151186555752015101575151561113741057125533551010105510101057551033321050501050701551055</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
